--- a/学生成绩模板.xlsx
+++ b/学生成绩模板.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kin9/python_code/score analysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1F62666-7061-CF4F-BA4C-E702ED1D99B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68AA4844-F69E-AC4A-9AA3-5485A1F5DCF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4440" yWindow="760" windowWidth="24960" windowHeight="17200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="160" yWindow="920" windowWidth="29080" windowHeight="16900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -41,66 +41,6 @@
     <t>总分</t>
   </si>
   <si>
-    <t>总分年级排名</t>
-  </si>
-  <si>
-    <t>总分集团排名</t>
-  </si>
-  <si>
-    <t>语文</t>
-  </si>
-  <si>
-    <t>语文年级排名</t>
-  </si>
-  <si>
-    <t>语文集团排名</t>
-  </si>
-  <si>
-    <t>数学</t>
-  </si>
-  <si>
-    <t>数学年级排名</t>
-  </si>
-  <si>
-    <t>数学集团排名</t>
-  </si>
-  <si>
-    <t>英语</t>
-  </si>
-  <si>
-    <t>英语年级排名</t>
-  </si>
-  <si>
-    <t>英语集团排名</t>
-  </si>
-  <si>
-    <t>物理</t>
-  </si>
-  <si>
-    <t>物理年级排名</t>
-  </si>
-  <si>
-    <t>物理集团排名</t>
-  </si>
-  <si>
-    <t>化学</t>
-  </si>
-  <si>
-    <t>化学年级排名</t>
-  </si>
-  <si>
-    <t>化学集团排名</t>
-  </si>
-  <si>
-    <t>生物</t>
-  </si>
-  <si>
-    <t>生物年级排名</t>
-  </si>
-  <si>
-    <t>生物集团排名</t>
-  </si>
-  <si>
     <t>林子桓</t>
   </si>
   <si>
@@ -249,6 +189,86 @@
   </si>
   <si>
     <t>李昀珊</t>
+  </si>
+  <si>
+    <t>总分年级排名_</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>总分集团排名_</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>语文_</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>语文年级排名_</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>语文集团排名_</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>数学_</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>数学年级排名_</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>数学集团排名_</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>英语_</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>英语年级排名_</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>英语集团排名_</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>物理_</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>物理年级排名_</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>物理集团排名_</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>化学_</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>化学年级排名_</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>化学集团排名_</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>生物_</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>生物年级排名_</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>生物集团排名_</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -671,69 +691,69 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>52</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
+        <v>53</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>4</v>
+        <v>54</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>6</v>
+        <v>56</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>7</v>
+        <v>57</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>8</v>
+        <v>58</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>9</v>
+        <v>59</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>11</v>
+        <v>61</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>12</v>
+        <v>62</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>13</v>
+        <v>63</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>14</v>
+        <v>64</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>15</v>
+        <v>65</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>17</v>
+        <v>67</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>18</v>
+        <v>68</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>19</v>
+        <v>69</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>21</v>
+        <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:22">
       <c r="A2" s="2" t="s">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="B2" s="2">
         <v>626</v>
@@ -801,7 +821,7 @@
     </row>
     <row r="3" spans="1:22">
       <c r="A3" s="2" t="s">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="B3" s="2">
         <v>607</v>
@@ -869,7 +889,7 @@
     </row>
     <row r="4" spans="1:22">
       <c r="A4" s="2" t="s">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="B4" s="2">
         <v>604.5</v>
@@ -937,7 +957,7 @@
     </row>
     <row r="5" spans="1:22">
       <c r="A5" s="2" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="B5" s="2">
         <v>601</v>
@@ -1005,7 +1025,7 @@
     </row>
     <row r="6" spans="1:22">
       <c r="A6" s="2" t="s">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="B6" s="2">
         <v>594.5</v>
@@ -1073,7 +1093,7 @@
     </row>
     <row r="7" spans="1:22">
       <c r="A7" s="2" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="B7" s="2">
         <v>594</v>
@@ -1141,7 +1161,7 @@
     </row>
     <row r="8" spans="1:22">
       <c r="A8" s="2" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="B8" s="2">
         <v>591</v>
@@ -1209,7 +1229,7 @@
     </row>
     <row r="9" spans="1:22">
       <c r="A9" s="2" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="B9" s="2">
         <v>588.5</v>
@@ -1277,7 +1297,7 @@
     </row>
     <row r="10" spans="1:22">
       <c r="A10" s="2" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="B10" s="2">
         <v>588</v>
@@ -1345,7 +1365,7 @@
     </row>
     <row r="11" spans="1:22">
       <c r="A11" s="2" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="B11" s="2">
         <v>582.5</v>
@@ -1413,7 +1433,7 @@
     </row>
     <row r="12" spans="1:22">
       <c r="A12" s="2" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="B12" s="2">
         <v>580.5</v>
@@ -1481,7 +1501,7 @@
     </row>
     <row r="13" spans="1:22">
       <c r="A13" s="2" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="B13" s="2">
         <v>578</v>
@@ -1549,7 +1569,7 @@
     </row>
     <row r="14" spans="1:22">
       <c r="A14" s="2" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="B14" s="2">
         <v>577.5</v>
@@ -1617,7 +1637,7 @@
     </row>
     <row r="15" spans="1:22">
       <c r="A15" s="2" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="B15" s="2">
         <v>574</v>
@@ -1685,7 +1705,7 @@
     </row>
     <row r="16" spans="1:22">
       <c r="A16" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="B16" s="2">
         <v>572.5</v>
@@ -1753,7 +1773,7 @@
     </row>
     <row r="17" spans="1:22">
       <c r="A17" s="2" t="s">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="B17" s="2">
         <v>572.5</v>
@@ -1821,7 +1841,7 @@
     </row>
     <row r="18" spans="1:22">
       <c r="A18" s="2" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="B18" s="2">
         <v>571</v>
@@ -1889,7 +1909,7 @@
     </row>
     <row r="19" spans="1:22">
       <c r="A19" s="2" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="B19" s="2">
         <v>567</v>
@@ -1957,7 +1977,7 @@
     </row>
     <row r="20" spans="1:22">
       <c r="A20" s="2" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="B20" s="2">
         <v>565.5</v>
@@ -2025,7 +2045,7 @@
     </row>
     <row r="21" spans="1:22">
       <c r="A21" s="2" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="B21" s="2">
         <v>564</v>
@@ -2093,7 +2113,7 @@
     </row>
     <row r="22" spans="1:22">
       <c r="A22" s="2" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="B22" s="2">
         <v>563.5</v>
@@ -2161,7 +2181,7 @@
     </row>
     <row r="23" spans="1:22">
       <c r="A23" s="2" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="B23" s="2">
         <v>563</v>
@@ -2229,7 +2249,7 @@
     </row>
     <row r="24" spans="1:22">
       <c r="A24" s="2" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="B24" s="2">
         <v>563</v>
@@ -2297,7 +2317,7 @@
     </row>
     <row r="25" spans="1:22">
       <c r="A25" s="2" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="B25" s="2">
         <v>563</v>
@@ -2365,7 +2385,7 @@
     </row>
     <row r="26" spans="1:22">
       <c r="A26" s="2" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="B26" s="2">
         <v>562.5</v>
@@ -2433,7 +2453,7 @@
     </row>
     <row r="27" spans="1:22">
       <c r="A27" s="2" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="B27" s="2">
         <v>562</v>
@@ -2501,7 +2521,7 @@
     </row>
     <row r="28" spans="1:22">
       <c r="A28" s="2" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="B28" s="2">
         <v>561</v>
@@ -2569,7 +2589,7 @@
     </row>
     <row r="29" spans="1:22">
       <c r="A29" s="2" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="B29" s="2">
         <v>560</v>
@@ -2637,7 +2657,7 @@
     </row>
     <row r="30" spans="1:22">
       <c r="A30" s="2" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="B30" s="2">
         <v>557.5</v>
@@ -2705,7 +2725,7 @@
     </row>
     <row r="31" spans="1:22">
       <c r="A31" s="2" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="B31" s="2">
         <v>556.5</v>
@@ -2773,7 +2793,7 @@
     </row>
     <row r="32" spans="1:22">
       <c r="A32" s="2" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="B32" s="2">
         <v>552</v>
@@ -2841,7 +2861,7 @@
     </row>
     <row r="33" spans="1:22">
       <c r="A33" s="2" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="B33" s="2">
         <v>550</v>
@@ -2909,7 +2929,7 @@
     </row>
     <row r="34" spans="1:22">
       <c r="A34" s="2" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="B34" s="2">
         <v>548.5</v>
@@ -2977,7 +2997,7 @@
     </row>
     <row r="35" spans="1:22">
       <c r="A35" s="2" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="B35" s="2">
         <v>548.5</v>
@@ -3045,7 +3065,7 @@
     </row>
     <row r="36" spans="1:22">
       <c r="A36" s="2" t="s">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="B36" s="2">
         <v>546</v>
@@ -3113,7 +3133,7 @@
     </row>
     <row r="37" spans="1:22">
       <c r="A37" s="2" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="B37" s="2">
         <v>545</v>
@@ -3181,7 +3201,7 @@
     </row>
     <row r="38" spans="1:22">
       <c r="A38" s="2" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="B38" s="2">
         <v>544.5</v>
@@ -3249,7 +3269,7 @@
     </row>
     <row r="39" spans="1:22">
       <c r="A39" s="2" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="B39" s="2">
         <v>544</v>
@@ -3317,7 +3337,7 @@
     </row>
     <row r="40" spans="1:22">
       <c r="A40" s="2" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="B40" s="2">
         <v>541</v>
@@ -3385,7 +3405,7 @@
     </row>
     <row r="41" spans="1:22">
       <c r="A41" s="2" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="B41" s="2">
         <v>539.5</v>
@@ -3453,7 +3473,7 @@
     </row>
     <row r="42" spans="1:22">
       <c r="A42" s="2" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="B42" s="2">
         <v>537.5</v>
@@ -3521,7 +3541,7 @@
     </row>
     <row r="43" spans="1:22">
       <c r="A43" s="2" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="B43" s="2">
         <v>534</v>
@@ -3589,7 +3609,7 @@
     </row>
     <row r="44" spans="1:22">
       <c r="A44" s="2" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="B44" s="2">
         <v>531</v>
@@ -3657,7 +3677,7 @@
     </row>
     <row r="45" spans="1:22">
       <c r="A45" s="2" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="B45" s="2">
         <v>530</v>
@@ -3725,7 +3745,7 @@
     </row>
     <row r="46" spans="1:22">
       <c r="A46" s="2" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="B46" s="2">
         <v>515.5</v>
@@ -3793,7 +3813,7 @@
     </row>
     <row r="47" spans="1:22">
       <c r="A47" s="2" t="s">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="B47" s="2">
         <v>508.5</v>
@@ -3861,7 +3881,7 @@
     </row>
     <row r="48" spans="1:22">
       <c r="A48" s="2" t="s">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="B48" s="2">
         <v>507</v>
@@ -3929,7 +3949,7 @@
     </row>
     <row r="49" spans="1:22">
       <c r="A49" s="2" t="s">
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="B49" s="2">
         <v>499.5</v>
@@ -3997,7 +4017,7 @@
     </row>
     <row r="50" spans="1:22">
       <c r="A50" s="2" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="B50" s="2">
         <v>492</v>
@@ -4065,7 +4085,7 @@
     </row>
     <row r="51" spans="1:22">
       <c r="A51" s="2" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="B51" s="2">
         <v>478.5</v>
